--- a/reports/pdf_change_20260930.xlsx
+++ b/reports/pdf_change_20260930.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,977억   ·   현금 21억(0.4%)      당일 2026-09-30  vs  전영업일 2026-09-29      매수 3종목  /  매도 3종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,977억      당일 2026-09-30  vs  전영업일 2026-09-29      매수 3종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -795,7 +795,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,259억   ·   현금 38억(1.2%)      당일 2026-09-30  vs  전영업일 2026-09-29      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,259억      당일 2026-09-30  vs  전영업일 2026-09-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -819,7 +819,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,697억   ·   현금 43억(1.6%)      당일 2026-09-30  vs  전영업일 2026-09-29      매수 0종목  /  매도 0종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,697억      당일 2026-09-30  vs  전영업일 2026-09-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -843,7 +843,7 @@
     <row r="16" ht="19" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억   ·   현금 11억(0.5%)      당일 2026-09-30  vs  전영업일 2026-09-29      매수 4종목  /  매도 1종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 1,983억      당일 2026-09-30  vs  전영업일 2026-09-29      매수 4종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B16" s="4" t="n"/>
@@ -1060,7 +1060,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 305억   ·   현금 1억(0.5%)      당일 2026-09-30  vs  전영업일 2026-09-29      매수 4종목  /  매도 3종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 305억      당일 2026-09-30  vs  전영업일 2026-09-29      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1309,7 +1309,7 @@
     <row r="32" ht="19" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억   ·   현금 8억(1.6%)      당일 2026-09-30  vs  전영업일 2026-09-29      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 475억      당일 2026-09-30  vs  전영업일 2026-09-29      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B32" s="4" t="n"/>
